--- a/artfynd/Stensjöåsen artfynd.xlsx
+++ b/artfynd/Stensjöåsen artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88637973</v>
+        <v>88638013</v>
       </c>
       <c r="B2" t="n">
-        <v>92727</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>678827</v>
+        <v>678698</v>
       </c>
       <c r="R2" t="n">
-        <v>7103976</v>
+        <v>7104190</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88637989</v>
+        <v>88637979</v>
       </c>
       <c r="B3" t="n">
-        <v>5492</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,28 +791,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>678734</v>
+        <v>678706</v>
       </c>
       <c r="R3" t="n">
-        <v>7104265</v>
+        <v>7104263</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,37 +885,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88637967</v>
+        <v>88637989</v>
       </c>
       <c r="B4" t="n">
-        <v>91210</v>
+        <v>5495</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>101410</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>678865</v>
+        <v>678734</v>
       </c>
       <c r="R4" t="n">
-        <v>7104071</v>
+        <v>7104265</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88638040</v>
+        <v>88638038</v>
       </c>
       <c r="B5" t="n">
-        <v>92529</v>
+        <v>5495</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,26 +1003,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>101410</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1030,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>678832</v>
+        <v>678700</v>
       </c>
       <c r="R5" t="n">
-        <v>7104049</v>
+        <v>7104108</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88637963</v>
+        <v>88638031</v>
       </c>
       <c r="B6" t="n">
-        <v>91406</v>
+        <v>79917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>678858</v>
+        <v>678694</v>
       </c>
       <c r="R6" t="n">
-        <v>7103986</v>
+        <v>7104186</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,32 +1204,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88638008</v>
+        <v>88637963</v>
       </c>
       <c r="B7" t="n">
-        <v>92547</v>
+        <v>92083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>678925</v>
+        <v>678858</v>
       </c>
       <c r="R7" t="n">
-        <v>7103899</v>
+        <v>7103986</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,32 +1309,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88637978</v>
+        <v>88637958</v>
       </c>
       <c r="B8" t="n">
-        <v>92565</v>
+        <v>90932</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>232140</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>678831</v>
+        <v>678877</v>
       </c>
       <c r="R8" t="n">
-        <v>7103976</v>
+        <v>7104118</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,32 +1414,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88638006</v>
+        <v>88637973</v>
       </c>
       <c r="B9" t="n">
-        <v>92547</v>
+        <v>91962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1450,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>678945</v>
+        <v>678827</v>
       </c>
       <c r="R9" t="n">
-        <v>7103994</v>
+        <v>7103976</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88638038</v>
+        <v>88638040</v>
       </c>
       <c r="B10" t="n">
-        <v>5492</v>
+        <v>93191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1528,28 +1530,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101410</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>678700</v>
+        <v>678832</v>
       </c>
       <c r="R10" t="n">
-        <v>7104108</v>
+        <v>7104049</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,11 +1627,11 @@
         <v>88637952</v>
       </c>
       <c r="B11" t="n">
-        <v>92535</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1729,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>88637958</v>
+        <v>88638000</v>
       </c>
       <c r="B12" t="n">
-        <v>90283</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1740,21 +1740,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>678877</v>
+        <v>678960</v>
       </c>
       <c r="R12" t="n">
-        <v>7104118</v>
+        <v>7103942</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,32 +1834,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>88637979</v>
+        <v>88638006</v>
       </c>
       <c r="B13" t="n">
-        <v>92535</v>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>678706</v>
+        <v>678945</v>
       </c>
       <c r="R13" t="n">
-        <v>7104263</v>
+        <v>7103994</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>88638013</v>
+        <v>88638008</v>
       </c>
       <c r="B14" t="n">
-        <v>78647</v>
+        <v>93209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>678698</v>
+        <v>678925</v>
       </c>
       <c r="R14" t="n">
-        <v>7104190</v>
+        <v>7103899</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,10 +2044,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>88638000</v>
+        <v>88637967</v>
       </c>
       <c r="B15" t="n">
-        <v>92535</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,21 +2055,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2082,10 +2082,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>678960</v>
+        <v>678865</v>
       </c>
       <c r="R15" t="n">
-        <v>7103942</v>
+        <v>7104071</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,32 +2149,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>88638031</v>
+        <v>88637978</v>
       </c>
       <c r="B16" t="n">
-        <v>79569</v>
+        <v>93228</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>232140</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>678694</v>
+        <v>678831</v>
       </c>
       <c r="R16" t="n">
-        <v>7104186</v>
+        <v>7103976</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2257,7 +2257,7 @@
         <v>126380533</v>
       </c>
       <c r="B17" t="n">
-        <v>78738</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
